--- a/docs/downloads/04/tbl_cm_educ_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_cm_educ_alaotra_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -387,12 +387,6 @@
           <t>Inconnu</t>
         </is>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>3.2</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -492,32 +486,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D8">
-        <v>8.800000000000001</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Alaotra - Ambodivoara</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D9">
-        <v>2.9</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="10">
@@ -528,14 +522,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="C10">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="D10">
-        <v>8.6</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="11">
@@ -546,14 +540,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="C11">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="D11">
-        <v>53.4</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="12">
@@ -564,50 +558,50 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="C12">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D12">
-        <v>22.4</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="C13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D13">
-        <v>13.8</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="D14">
-        <v>1.7</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="15">
@@ -618,14 +612,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="C15">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D15">
-        <v>13.5</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="16">
@@ -636,50 +630,44 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="C16">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="D16">
-        <v>55.8</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="C17">
-        <v>11</v>
-      </c>
-      <c r="D17">
-        <v>21.2</v>
+          <t>Inconnu</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="C18">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="D18">
-        <v>9.6</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="19">
@@ -690,14 +678,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="C19">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D19">
-        <v>6.5</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="20">
@@ -708,68 +696,62 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="C20">
-        <v>28</v>
-      </c>
-      <c r="D20">
-        <v>60.9</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="C21">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D21">
-        <v>26.1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="D22">
-        <v>2.2</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D23">
-        <v>4.3</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="24">
@@ -780,68 +762,68 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="C24">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D24">
-        <v>10</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="C25">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="D25">
-        <v>61.1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="C26">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="D26">
-        <v>22.2</v>
+        <v>60.7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="C27">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D27">
-        <v>6.7</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="28">
@@ -852,92 +834,86 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="C28">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D28">
-        <v>18</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="C29">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="D29">
-        <v>60.7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="C30">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="D30">
-        <v>14.6</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="C31">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D31">
-        <v>5.6</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Universitaire</t>
-        </is>
-      </c>
-      <c r="C32">
-        <v>1</v>
-      </c>
-      <c r="D32">
-        <v>1.1</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -946,16 +922,16 @@
         </is>
       </c>
       <c r="C33">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="D33">
-        <v>6.8</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -964,16 +940,16 @@
         </is>
       </c>
       <c r="C34">
-        <v>51</v>
+        <v>307</v>
       </c>
       <c r="D34">
-        <v>69.90000000000001</v>
+        <v>60.6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -982,118 +958,28 @@
         </is>
       </c>
       <c r="C35">
-        <v>14</v>
+        <v>109</v>
       </c>
       <c r="D35">
-        <v>19.2</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="C36">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="D36">
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="C37">
-        <v>51</v>
-      </c>
-      <c r="D37">
-        <v>10.1</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="C38">
-        <v>307</v>
-      </c>
-      <c r="D38">
-        <v>60.6</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="C39">
-        <v>109</v>
-      </c>
-      <c r="D39">
-        <v>21.5</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="C40">
-        <v>34</v>
-      </c>
-      <c r="D40">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Universitaire</t>
-        </is>
-      </c>
-      <c r="C41">
-        <v>6</v>
-      </c>
-      <c r="D41">
-        <v>1.2</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/04/tbl_cm_educ_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_cm_educ_alaotra_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,7 +384,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
     </row>
@@ -435,12 +435,6 @@
           <t>Inconnu</t>
         </is>
       </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-      <c r="D5">
-        <v>7.4</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -450,14 +444,8 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="C6">
-        <v>40</v>
-      </c>
-      <c r="D6">
-        <v>58.8</v>
+          <t>Non scolarisé</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -468,14 +456,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="C7">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="D7">
-        <v>22.1</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="8">
@@ -486,32 +474,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="C8">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D8">
-        <v>11.8</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Alaotra - Ambatomanga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="C9">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D9">
-        <v>8.6</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="10">
@@ -522,14 +510,8 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="C10">
-        <v>31</v>
-      </c>
-      <c r="D10">
-        <v>53.4</v>
+          <t>Inconnu</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -540,14 +522,8 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="C11">
-        <v>13</v>
-      </c>
-      <c r="D11">
-        <v>22.4</v>
+          <t>Non scolarisé</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -558,50 +534,50 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="C12">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="D12">
-        <v>15.5</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Ambodivoara</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D13">
-        <v>13.5</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Ambodivoara</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="C14">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="D14">
-        <v>55.8</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="15">
@@ -612,14 +588,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="C15">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D15">
-        <v>21.2</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="16">
@@ -630,44 +606,50 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="C16">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="D16">
-        <v>9.6</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
+          <t>Secondaire 1er cycle</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>11</v>
+      </c>
+      <c r="D17">
+        <v>21.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="C18">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="D18">
-        <v>60.9</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="19">
@@ -678,14 +660,8 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="C19">
-        <v>12</v>
-      </c>
-      <c r="D19">
-        <v>26.1</v>
+          <t>Non scolarisé</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -696,44 +672,44 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
-        </is>
+          <t>Primaire</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>28</v>
+      </c>
+      <c r="D20">
+        <v>60.9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="C21">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D21">
-        <v>10</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="C22">
-        <v>55</v>
-      </c>
-      <c r="D22">
-        <v>61.1</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -744,14 +720,8 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="C23">
-        <v>20</v>
-      </c>
-      <c r="D23">
-        <v>22.2</v>
+          <t>Inconnu</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -762,68 +732,68 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="C24">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D24">
-        <v>6.7</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="C25">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="D25">
-        <v>18</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="C26">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="D26">
-        <v>60.7</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="C27">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D27">
-        <v>14.6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="28">
@@ -834,38 +804,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="C28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D28">
-        <v>6.7</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="C29">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D29">
-        <v>6.8</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -874,16 +844,16 @@
         </is>
       </c>
       <c r="C30">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D30">
-        <v>69.90000000000001</v>
+        <v>60.7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -892,93 +862,189 @@
         </is>
       </c>
       <c r="C31">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D31">
-        <v>19.2</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
+      </c>
+      <c r="C32">
+        <v>6</v>
+      </c>
+      <c r="D32">
+        <v>6.7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Inconnu</t>
         </is>
-      </c>
-      <c r="C33">
-        <v>51</v>
-      </c>
-      <c r="D33">
-        <v>10.1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="C34">
-        <v>307</v>
-      </c>
-      <c r="D34">
-        <v>60.6</v>
+          <t>Non scolarisé</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="C35">
-        <v>109</v>
+        <v>51</v>
       </c>
       <c r="D35">
-        <v>21.5</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>Alaotra - Mangabe</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Secondaire 1er cycle</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>14</v>
+      </c>
+      <c r="D36">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Alaotra - Mangabe</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>Alaotra - Tous</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Inconnu</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>11</v>
+      </c>
+      <c r="D38">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Non scolarisé</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>40</v>
+      </c>
+      <c r="D39">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Primaire</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>307</v>
+      </c>
+      <c r="D40">
+        <v>60.6</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Secondaire 1er cycle</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>109</v>
+      </c>
+      <c r="D41">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
         <is>
           <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
-      <c r="C36">
+      <c r="C42">
         <v>40</v>
       </c>
-      <c r="D36">
+      <c r="D42">
         <v>7.9</v>
       </c>
     </row>

--- a/docs/downloads/04/tbl_cm_educ_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_cm_educ_alaotra_tous.xlsx
@@ -379,7 +379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -391,7 +391,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -409,7 +409,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -427,7 +427,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -439,7 +439,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -451,7 +451,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -469,7 +469,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -487,7 +487,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -505,7 +505,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -517,7 +517,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -529,7 +529,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -547,7 +547,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -565,7 +565,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -583,7 +583,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -601,7 +601,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -619,7 +619,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -637,7 +637,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -655,7 +655,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -667,7 +667,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -685,7 +685,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -703,7 +703,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -715,7 +715,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -727,7 +727,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -745,7 +745,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -763,7 +763,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -781,7 +781,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -817,7 +817,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -835,7 +835,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -853,7 +853,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -871,7 +871,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -889,7 +889,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -901,7 +901,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -913,7 +913,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -931,7 +931,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -949,7 +949,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -979,7 +979,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -997,7 +997,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1015,7 +1015,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1033,7 +1033,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
